--- a/artfynd/A 54692-2024 artfynd.xlsx
+++ b/artfynd/A 54692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116452</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Ekokryss</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954224</t>
         </is>
       </c>
     </row>
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92915133</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954243</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,6 +1410,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954235</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954241</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1737,6 +1782,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1852,6 +1902,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Ekokryss</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954227</t>
         </is>
       </c>
     </row>
@@ -1964,6 +2019,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92915138</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2084,6 +2144,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116453</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2204,6 +2269,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116455</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2329,6 +2399,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116458</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2449,6 +2524,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116456</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2564,6 +2644,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116461</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2681,6 +2766,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954239</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2801,6 +2891,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116451</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2921,6 +3016,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954270</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3041,6 +3141,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954264</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3161,6 +3266,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116470</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3284,6 +3394,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91314556</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3404,6 +3519,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954258</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3524,6 +3644,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954263</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3644,6 +3769,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954285</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3764,6 +3894,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95116472</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3884,6 +4019,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954289</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4004,6 +4144,11 @@
           <t>Ekokryss</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954247</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4117,6 +4262,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72449051</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4227,6 +4377,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65413056</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4343,6 +4498,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70783305</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4459,6 +4619,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70783300</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4581,8 +4746,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72456859</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>